--- a/cet4/result/70_医道女神_白衣天使的守护/70_医道女神_白衣天使的守护_学习版.xlsx
+++ b/cet4/result/70_医道女神_白衣天使的守护/70_医道女神_白衣天使的守护_学习版.xlsx
@@ -397,731 +397,577 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D40"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>surface</v>
       </c>
       <c r="B2" t="str">
-        <v>surface</v>
+        <v>/ˈsɜːrfɪs/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>表面</v>
       </c>
-      <c r="D2" t="str">
-        <v>surface(表面)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>son</v>
       </c>
       <c r="B3" t="str">
-        <v>son</v>
+        <v>/sʌn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>儿子</v>
       </c>
-      <c r="D3" t="str">
-        <v>son(儿子)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>single</v>
       </c>
       <c r="B4" t="str">
-        <v>single</v>
+        <v>/ˈsɪŋɡl/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>单一</v>
       </c>
-      <c r="D4" t="str">
-        <v>single(单一)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>universal</v>
       </c>
       <c r="B5" t="str">
-        <v>universal</v>
+        <v>/ˌjuːnɪˈvɜːrsl/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>普遍</v>
       </c>
-      <c r="D5" t="str">
-        <v>universal(普遍)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>household</v>
       </c>
       <c r="B6" t="str">
-        <v>household</v>
+        <v>/ˈhaʊshoʊld/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>家庭</v>
       </c>
-      <c r="D6" t="str">
-        <v>household(家庭)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>arrive</v>
       </c>
       <c r="B7" t="str">
-        <v>arrive</v>
+        <v>/əˈraɪv/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>到达</v>
       </c>
-      <c r="D7" t="str">
-        <v>arrive(到达)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>community</v>
       </c>
       <c r="B8" t="str">
-        <v>community</v>
+        <v>/kəˈmjuːnəti/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>社区</v>
       </c>
-      <c r="D8" t="str">
-        <v>community(社区)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>substantial</v>
       </c>
       <c r="B9" t="str">
-        <v>substantial</v>
+        <v>/səbˈstænʃl/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>大量</v>
       </c>
-      <c r="D9" t="str">
-        <v>substantial(大量)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>Mister</v>
       </c>
       <c r="B10" t="str">
-        <v>Mister</v>
+        <v>/ˈmɪstər/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>先生</v>
       </c>
-      <c r="D10" t="str">
-        <v>Mister(先生)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>vigorous</v>
       </c>
       <c r="B11" t="str">
-        <v>vigorous</v>
+        <v>/ˈvɪɡərəs/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>有力</v>
       </c>
-      <c r="D11" t="str">
-        <v>vigorous(有力)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>stand</v>
       </c>
       <c r="B12" t="str">
-        <v>stand</v>
+        <v>/stænd/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>站立</v>
       </c>
-      <c r="D12" t="str">
-        <v>stand(站立)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>dust</v>
       </c>
       <c r="B13" t="str">
-        <v>household</v>
+        <v>/dʌst/</v>
       </c>
       <c r="C13" t="str">
-        <v>家庭</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D13" t="str">
-        <v>household(家庭)📢</v>
+        <v>灰尘</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>excessive</v>
       </c>
       <c r="B14" t="str">
-        <v>dust</v>
+        <v>/ɪkˈsesɪv/</v>
       </c>
       <c r="C14" t="str">
-        <v>灰尘</v>
+        <v>adj.</v>
       </c>
       <c r="D14" t="str">
-        <v>dust(灰尘)📢</v>
+        <v>过多</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>drug</v>
       </c>
       <c r="B15" t="str">
-        <v>excessive</v>
+        <v>/drʌɡ/</v>
       </c>
       <c r="C15" t="str">
-        <v>过多</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D15" t="str">
-        <v>excessive(过多)📢</v>
+        <v>药物</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>discussion</v>
       </c>
       <c r="B16" t="str">
-        <v>drug</v>
+        <v>/dɪˈskʌʃn/</v>
       </c>
       <c r="C16" t="str">
-        <v>药物</v>
+        <v>n.</v>
       </c>
       <c r="D16" t="str">
-        <v>drug(药物)📢</v>
+        <v>讨论</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>costly</v>
       </c>
       <c r="B17" t="str">
-        <v>discussion</v>
+        <v>/ˈkɔːstli/</v>
       </c>
       <c r="C17" t="str">
-        <v>讨论</v>
+        <v>n./adj.</v>
       </c>
       <c r="D17" t="str">
-        <v>discussion(讨论)📢</v>
+        <v>昂贵</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>splendid</v>
       </c>
       <c r="B18" t="str">
-        <v>costly</v>
+        <v>/ˈsplendɪd/</v>
       </c>
       <c r="C18" t="str">
-        <v>昂贵</v>
+        <v>adj.</v>
       </c>
       <c r="D18" t="str">
-        <v>costly(昂贵)📢</v>
+        <v>辉煌</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>idle</v>
       </c>
       <c r="B19" t="str">
-        <v>vigorous</v>
+        <v>/ˈaɪdl/</v>
       </c>
       <c r="C19" t="str">
-        <v>有力</v>
+        <v>vt./vi./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>vigorous(有力)📢</v>
+        <v>闲置</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>feedback</v>
       </c>
       <c r="B20" t="str">
-        <v>splendid</v>
+        <v>/ˈfiːdbæk/</v>
       </c>
       <c r="C20" t="str">
-        <v>辉煌</v>
+        <v>n.</v>
       </c>
       <c r="D20" t="str">
-        <v>splendid(辉煌)📢</v>
+        <v>反馈</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>survive</v>
       </c>
       <c r="B21" t="str">
-        <v>costly</v>
+        <v>/sərˈvaɪv/</v>
       </c>
       <c r="C21" t="str">
-        <v>代价高</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>costly(代价高)📢</v>
+        <v>幸存</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>preserve</v>
       </c>
       <c r="B22" t="str">
-        <v>idle</v>
+        <v>/prɪˈzɜːrv/</v>
       </c>
       <c r="C22" t="str">
-        <v>闲置</v>
+        <v>n./vt.</v>
       </c>
       <c r="D22" t="str">
-        <v>idle(闲置)📢</v>
+        <v>保护</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>investigation</v>
       </c>
       <c r="B23" t="str">
-        <v>feedback</v>
+        <v>/ɪnˌvestɪˈɡeɪʃn/</v>
       </c>
       <c r="C23" t="str">
-        <v>反馈</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>feedback(反馈)📢</v>
+        <v>调查</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>correspond</v>
       </c>
       <c r="B24" t="str">
-        <v>survive</v>
+        <v>/ˌkɔːrəˈspɑːnd/</v>
       </c>
       <c r="C24" t="str">
-        <v>幸存</v>
+        <v>vi.</v>
       </c>
       <c r="D24" t="str">
-        <v>survive(幸存)📢</v>
+        <v>通信</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>back</v>
       </c>
       <c r="B25" t="str">
-        <v>excessive</v>
+        <v>/bæk/</v>
       </c>
       <c r="C25" t="str">
-        <v>过多</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D25" t="str">
-        <v>excessive(过多)📢</v>
+        <v>向后</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>movement</v>
       </c>
       <c r="B26" t="str">
-        <v>preserve</v>
+        <v>/ˈmuːvmənt/</v>
       </c>
       <c r="C26" t="str">
-        <v>保护</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>preserve(保护)📢</v>
+        <v>运动</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>radioactive</v>
       </c>
       <c r="B27" t="str">
-        <v>investigation</v>
+        <v>/ˌreɪdioʊˈæktɪv/</v>
       </c>
       <c r="C27" t="str">
-        <v>调查</v>
+        <v>adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>investigation(调查)📢</v>
+        <v>放射性</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>proper</v>
       </c>
       <c r="B28" t="str">
-        <v>vigorous</v>
+        <v>/ˈprɑːpər/</v>
       </c>
       <c r="C28" t="str">
-        <v>有力</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>vigorous(有力)📢</v>
+        <v>适当</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>channel</v>
       </c>
       <c r="B29" t="str">
-        <v>correspond</v>
+        <v>/ˈtʃænl/</v>
       </c>
       <c r="C29" t="str">
-        <v>通信</v>
+        <v>n./vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>correspond(通信)📢</v>
+        <v>渠道</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>earn</v>
       </c>
       <c r="B30" t="str">
-        <v>back</v>
+        <v>/ɜːrn/</v>
       </c>
       <c r="C30" t="str">
-        <v>向后</v>
+        <v>n./vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>back(向后)📢</v>
+        <v>赚</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>topic</v>
       </c>
       <c r="B31" t="str">
-        <v>movement</v>
+        <v>/ˈtɑːpɪk/</v>
       </c>
       <c r="C31" t="str">
-        <v>运动</v>
+        <v>n.</v>
       </c>
       <c r="D31" t="str">
-        <v>movement(运动)📢</v>
+        <v>主题</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>reader</v>
       </c>
       <c r="B32" t="str">
-        <v>radioactive</v>
+        <v>/ˈriːdər/</v>
       </c>
       <c r="C32" t="str">
-        <v>放射性</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>radioactive(放射性)📢</v>
+        <v>读者</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>learned</v>
       </c>
       <c r="B33" t="str">
-        <v>proper</v>
+        <v>/ˈlɜːrnɪd/</v>
       </c>
       <c r="C33" t="str">
-        <v>适当</v>
+        <v>adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>proper(适当)📢</v>
+        <v>有学问</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>cup</v>
       </c>
       <c r="B34" t="str">
-        <v>splendid</v>
+        <v>/kʌp/</v>
       </c>
       <c r="C34" t="str">
-        <v>辉煌</v>
+        <v>n./vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>splendid(辉煌)📢</v>
+        <v>杯子</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>skill</v>
       </c>
       <c r="B35" t="str">
-        <v>channel</v>
+        <v>/skɪl/</v>
       </c>
       <c r="C35" t="str">
-        <v>渠道</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>channel(渠道)📢</v>
+        <v>技能</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>manner</v>
       </c>
       <c r="B36" t="str">
-        <v>splendid</v>
+        <v>/ˈmænər/</v>
       </c>
       <c r="C36" t="str">
-        <v>极好</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>splendid(极好)📢</v>
+        <v>方式</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>flour</v>
       </c>
       <c r="B37" t="str">
-        <v>earn</v>
+        <v>/ˈflaʊər/</v>
       </c>
       <c r="C37" t="str">
-        <v>赚</v>
+        <v>n./vt.</v>
       </c>
       <c r="D37" t="str">
-        <v>earn(赚)📢</v>
+        <v>面粉</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>beer</v>
       </c>
       <c r="B38" t="str">
-        <v>topic</v>
+        <v>/bɪr/</v>
       </c>
       <c r="C38" t="str">
-        <v>主题</v>
+        <v>n./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>topic(主题)📢</v>
+        <v>啤酒</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>turkey</v>
       </c>
       <c r="B39" t="str">
-        <v>discussion</v>
+        <v>/ˈtɜːrki/</v>
       </c>
       <c r="C39" t="str">
-        <v>讨论</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>discussion(讨论)📢</v>
+        <v>火鸡</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>bet</v>
       </c>
       <c r="B40" t="str">
-        <v>reader</v>
+        <v>/bet/</v>
       </c>
       <c r="C40" t="str">
-        <v>读者</v>
+        <v>n./v.</v>
       </c>
       <c r="D40" t="str">
-        <v>reader(读者)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>learned</v>
-      </c>
-      <c r="C41" t="str">
-        <v>有学问</v>
-      </c>
-      <c r="D41" t="str">
-        <v>learned(有学问)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>learned</v>
-      </c>
-      <c r="C42" t="str">
-        <v>有学问</v>
-      </c>
-      <c r="D42" t="str">
-        <v>learned(有学问)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>excessive</v>
-      </c>
-      <c r="C43" t="str">
-        <v>过多</v>
-      </c>
-      <c r="D43" t="str">
-        <v>excessive(过多)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>cup</v>
-      </c>
-      <c r="C44" t="str">
-        <v>杯子</v>
-      </c>
-      <c r="D44" t="str">
-        <v>cup(杯子)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>skill</v>
-      </c>
-      <c r="C45" t="str">
-        <v>技能</v>
-      </c>
-      <c r="D45" t="str">
-        <v>skill(技能)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>manner</v>
-      </c>
-      <c r="C46" t="str">
-        <v>方式</v>
-      </c>
-      <c r="D46" t="str">
-        <v>manner(方式)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>flour</v>
-      </c>
-      <c r="C47" t="str">
-        <v>面粉</v>
-      </c>
-      <c r="D47" t="str">
-        <v>flour(面粉)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>beer</v>
-      </c>
-      <c r="C48" t="str">
-        <v>啤酒</v>
-      </c>
-      <c r="D48" t="str">
-        <v>beer(啤酒)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>turkey</v>
-      </c>
-      <c r="C49" t="str">
-        <v>火鸡</v>
-      </c>
-      <c r="D49" t="str">
-        <v>turkey(火鸡)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>bet</v>
-      </c>
-      <c r="C50" t="str">
         <v>打赌</v>
-      </c>
-      <c r="D50" t="str">
-        <v>bet(打赌)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>splendid</v>
-      </c>
-      <c r="C51" t="str">
-        <v>极好</v>
-      </c>
-      <c r="D51" t="str">
-        <v>splendid(极好)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
   </ignoredErrors>
 </worksheet>
 </file>